--- a/output/竞品分析日报.xlsx
+++ b/output/竞品分析日报.xlsx
@@ -10490,11 +10490,7 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
           <t>—</t>
@@ -10502,7 +10498,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>0 → 0 → 0</t>
+          <t xml:space="preserve">0 → 0 → </t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -35166,13 +35162,21 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F884" t="inlineStr"/>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
       <c r="G884" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H884" t="inlineStr"/>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
       <c r="I884" t="inlineStr">
         <is>
           <t>2026-07-22</t>

--- a/output/竞品分析日报.xlsx
+++ b/output/竞品分析日报.xlsx
@@ -10490,7 +10490,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t>—</t>
@@ -10498,7 +10502,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 → 0 → </t>
+          <t>0 → 0 → 0</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">

--- a/output/竞品分析日报.xlsx
+++ b/output/竞品分析日报.xlsx
@@ -518,11 +518,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -561,11 +557,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -604,11 +596,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -647,11 +635,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -690,11 +674,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -733,11 +713,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -776,11 +752,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -819,11 +791,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -862,11 +830,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -905,11 +869,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1202,7 +1162,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1475,7 +1435,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1709,7 +1669,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2801,7 +2761,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3269,7 +3229,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3464,7 +3424,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4517,7 +4477,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Trekking Pole</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4595,7 +4555,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4790,7 +4750,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4829,7 +4789,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4868,7 +4828,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4907,7 +4867,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4946,7 +4906,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5102,7 +5062,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5921,7 +5881,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7091,7 +7051,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Pad</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7286,7 +7246,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7442,7 +7402,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -7481,7 +7441,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8222,7 +8182,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -8261,7 +8221,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8573,7 +8533,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Bag</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9314,7 +9274,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10211,7 +10171,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -10443,11 +10403,7 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
           <t>—</t>
@@ -10455,7 +10411,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>0 → 0 → 0</t>
+          <t>0 → 0</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -10492,7 +10448,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10502,7 +10458,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>0 → 0 → 0</t>
+          <t>0 → 0 → 5.0</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -10631,11 +10587,7 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
           <t>—</t>
@@ -10643,7 +10595,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>5.0 → 5.0 → 5.0</t>
+          <t>5.0 → 5.0</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11618,7 +11570,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -12203,7 +12155,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -15791,7 +15743,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -17819,7 +17771,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -18599,7 +18551,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Bag</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -18638,7 +18590,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Bag</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -18677,7 +18629,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Bag</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -18989,7 +18941,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -19028,7 +18980,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -19379,7 +19331,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -19574,7 +19526,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -20233,11 +20185,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H503" t="inlineStr"/>
       <c r="I503" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -20276,11 +20224,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H504" t="inlineStr"/>
       <c r="I504" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -20816,7 +20760,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Sleeping Bag</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -21947,7 +21891,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -22727,7 +22671,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -23663,7 +23607,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -24638,7 +24582,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -25145,7 +25089,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -27222,7 +27166,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>售罄</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -27261,7 +27205,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>售罄</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -33735,7 +33679,7 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>售罄</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="F848" t="inlineStr"/>
@@ -35401,21 +35345,13 @@
           <t>售罄</t>
         </is>
       </c>
-      <c r="F889" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
+      <c r="F889" t="inlineStr"/>
       <c r="G889" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H889" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
+      <c r="H889" t="inlineStr"/>
       <c r="I889" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -36028,7 +35964,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Trekking Pole</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -37081,7 +37017,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
@@ -38524,7 +38460,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D969" t="inlineStr">
@@ -38602,7 +38538,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -38641,7 +38577,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D972" t="inlineStr">
@@ -38680,7 +38616,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D973" t="inlineStr">
@@ -38758,7 +38694,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -38797,7 +38733,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D976" t="inlineStr">
@@ -38875,7 +38811,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -38914,7 +38850,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -39343,7 +39279,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -39733,7 +39669,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -40435,7 +40371,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -40474,7 +40410,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -44452,7 +44388,7 @@
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
@@ -45278,11 +45214,7 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="F1140" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
+      <c r="F1140" t="inlineStr"/>
       <c r="G1140" t="inlineStr">
         <is>
           <t>—</t>
@@ -45290,7 +45222,7 @@
       </c>
       <c r="H1140" t="inlineStr">
         <is>
-          <t>5.0 → 5.0 → 5.0</t>
+          <t>5.0 → 5.0</t>
         </is>
       </c>
       <c r="I1140" t="inlineStr">
@@ -50479,11 +50411,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1273" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1273" t="inlineStr"/>
       <c r="I1273" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -50550,7 +50478,7 @@
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1275" t="inlineStr">
@@ -50569,11 +50497,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1275" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1275" t="inlineStr"/>
       <c r="I1275" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -50593,7 +50517,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1276" t="inlineStr">
@@ -50612,11 +50536,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1276" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1276" t="inlineStr"/>
       <c r="I1276" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -50749,11 +50669,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1279" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1279" t="inlineStr"/>
       <c r="I1279" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -50839,11 +50755,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1281" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1281" t="inlineStr"/>
       <c r="I1281" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -50949,7 +50861,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1284" t="inlineStr">
@@ -51183,7 +51095,7 @@
       </c>
       <c r="C1290" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1290" t="inlineStr">
@@ -51339,7 +51251,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1294" t="inlineStr">
@@ -51378,7 +51290,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1295" t="inlineStr">
@@ -51612,7 +51524,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1301" t="inlineStr">
@@ -51651,7 +51563,7 @@
       </c>
       <c r="C1302" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1302" t="inlineStr">
@@ -51690,7 +51602,7 @@
       </c>
       <c r="C1303" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1303" t="inlineStr">
@@ -52509,7 +52421,7 @@
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1324" t="inlineStr">
@@ -52587,7 +52499,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1326" t="inlineStr">
@@ -52704,7 +52616,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1329" t="inlineStr">
@@ -52743,7 +52655,7 @@
       </c>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Bag</t>
         </is>
       </c>
       <c r="D1330" t="inlineStr">
@@ -53250,7 +53162,7 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1343" t="inlineStr">
@@ -53289,7 +53201,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1344" t="inlineStr">
@@ -53406,7 +53318,7 @@
       </c>
       <c r="C1347" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1347" t="inlineStr">
@@ -53445,7 +53357,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1348" t="inlineStr">
@@ -53523,7 +53435,7 @@
       </c>
       <c r="C1350" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1350" t="inlineStr">
@@ -53562,7 +53474,7 @@
       </c>
       <c r="C1351" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1351" t="inlineStr">
@@ -53601,7 +53513,7 @@
       </c>
       <c r="C1352" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1352" t="inlineStr">
@@ -53640,7 +53552,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1353" t="inlineStr">
@@ -53679,7 +53591,7 @@
       </c>
       <c r="C1354" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1354" t="inlineStr">
@@ -53718,7 +53630,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1355" t="inlineStr">
@@ -53757,7 +53669,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1356" t="inlineStr">
@@ -53796,7 +53708,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1357" t="inlineStr">
@@ -53835,7 +53747,7 @@
       </c>
       <c r="C1358" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1358" t="inlineStr">
@@ -53874,7 +53786,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1359" t="inlineStr">
@@ -53913,7 +53825,7 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1360" t="inlineStr">
@@ -53991,7 +53903,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1362" t="inlineStr">
@@ -54030,7 +53942,7 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1363" t="inlineStr">
@@ -54069,7 +53981,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1364" t="inlineStr">
@@ -54108,7 +54020,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1365" t="inlineStr">
@@ -54147,7 +54059,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1366" t="inlineStr">
@@ -54186,7 +54098,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1367" t="inlineStr">
@@ -54225,7 +54137,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1368" t="inlineStr">
@@ -54264,7 +54176,7 @@
       </c>
       <c r="C1369" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1369" t="inlineStr">
@@ -54303,7 +54215,7 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1370" t="inlineStr">
@@ -54342,7 +54254,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1371" t="inlineStr">
@@ -54381,7 +54293,7 @@
       </c>
       <c r="C1372" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1372" t="inlineStr">
@@ -54420,7 +54332,7 @@
       </c>
       <c r="C1373" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1373" t="inlineStr">
@@ -54459,7 +54371,7 @@
       </c>
       <c r="C1374" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1374" t="inlineStr">
@@ -54498,7 +54410,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1375" t="inlineStr">
@@ -54537,7 +54449,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1376" t="inlineStr">
@@ -54576,7 +54488,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1377" t="inlineStr">
@@ -54615,7 +54527,7 @@
       </c>
       <c r="C1378" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1378" t="inlineStr">
@@ -54654,7 +54566,7 @@
       </c>
       <c r="C1379" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1379" t="inlineStr">
@@ -54810,7 +54722,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1383" t="inlineStr">
@@ -54849,7 +54761,7 @@
       </c>
       <c r="C1384" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1384" t="inlineStr">
@@ -54888,7 +54800,7 @@
       </c>
       <c r="C1385" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1385" t="inlineStr">
@@ -54927,7 +54839,7 @@
       </c>
       <c r="C1386" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1386" t="inlineStr">
@@ -54966,7 +54878,7 @@
       </c>
       <c r="C1387" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1387" t="inlineStr">
@@ -55005,7 +54917,7 @@
       </c>
       <c r="C1388" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1388" t="inlineStr">
@@ -55044,7 +54956,7 @@
       </c>
       <c r="C1389" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1389" t="inlineStr">
@@ -55083,7 +54995,7 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1390" t="inlineStr">
@@ -55122,7 +55034,7 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
@@ -55161,7 +55073,7 @@
       </c>
       <c r="C1392" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1392" t="inlineStr">
@@ -55200,7 +55112,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1393" t="inlineStr">
@@ -55746,7 +55658,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1407" t="inlineStr">
@@ -55785,7 +55697,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr">
@@ -55824,7 +55736,7 @@
       </c>
       <c r="C1409" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1409" t="inlineStr">
@@ -55863,7 +55775,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1410" t="inlineStr">
@@ -55902,7 +55814,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1411" t="inlineStr">
@@ -55941,7 +55853,7 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="D1412" t="inlineStr">
@@ -56097,7 +56009,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1416" t="inlineStr">
@@ -56136,7 +56048,7 @@
       </c>
       <c r="C1417" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1417" t="inlineStr">
@@ -56175,7 +56087,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1418" t="inlineStr">
@@ -56214,7 +56126,7 @@
       </c>
       <c r="C1419" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1419" t="inlineStr">
@@ -56253,7 +56165,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -56292,7 +56204,7 @@
       </c>
       <c r="C1421" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1421" t="inlineStr">
@@ -56331,7 +56243,7 @@
       </c>
       <c r="C1422" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1422" t="inlineStr">
@@ -56370,7 +56282,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1423" t="inlineStr">
@@ -56409,7 +56321,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1424" t="inlineStr">
@@ -56448,7 +56360,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -56487,7 +56399,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1426" t="inlineStr">
@@ -56526,7 +56438,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1427" t="inlineStr">
@@ -56565,7 +56477,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1428" t="inlineStr">
@@ -56604,7 +56516,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1429" t="inlineStr">
@@ -56643,7 +56555,7 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1430" t="inlineStr">
@@ -56682,7 +56594,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1431" t="inlineStr">
@@ -56721,7 +56633,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1432" t="inlineStr">
@@ -56760,7 +56672,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1433" t="inlineStr">
@@ -56799,7 +56711,7 @@
       </c>
       <c r="C1434" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1434" t="inlineStr">
@@ -56838,7 +56750,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1435" t="inlineStr">
@@ -56877,7 +56789,7 @@
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1436" t="inlineStr">
@@ -56916,7 +56828,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1437" t="inlineStr">
@@ -56955,7 +56867,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1438" t="inlineStr">
@@ -56994,7 +56906,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1439" t="inlineStr">
@@ -57033,7 +56945,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1440" t="inlineStr">
@@ -57072,7 +56984,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1441" t="inlineStr">
@@ -57111,7 +57023,7 @@
       </c>
       <c r="C1442" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1442" t="inlineStr">
@@ -57150,7 +57062,7 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1443" t="inlineStr">
@@ -57189,7 +57101,7 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1444" t="inlineStr">
@@ -57228,7 +57140,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1445" t="inlineStr">
@@ -57267,7 +57179,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1446" t="inlineStr">
@@ -57306,7 +57218,7 @@
       </c>
       <c r="C1447" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1447" t="inlineStr">
@@ -57345,7 +57257,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1448" t="inlineStr">
@@ -57384,7 +57296,7 @@
       </c>
       <c r="C1449" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1449" t="inlineStr">
@@ -57423,7 +57335,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1450" t="inlineStr">
@@ -57462,7 +57374,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="D1451" t="inlineStr">
@@ -57540,7 +57452,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1453" t="inlineStr">
@@ -57579,7 +57491,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1454" t="inlineStr">
@@ -57618,7 +57530,7 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1455" t="inlineStr">
@@ -57657,7 +57569,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1456" t="inlineStr">
@@ -57735,7 +57647,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D1458" t="inlineStr">
@@ -57774,7 +57686,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -57813,7 +57725,7 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1460" t="inlineStr">
@@ -57852,7 +57764,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1461" t="inlineStr">
@@ -57891,7 +57803,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -57969,7 +57881,7 @@
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -58008,7 +57920,7 @@
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1465" t="inlineStr">
@@ -58086,7 +57998,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1467" t="inlineStr">
@@ -58125,7 +58037,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1468" t="inlineStr">
@@ -58671,7 +58583,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1482" t="inlineStr">
@@ -58710,7 +58622,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1483" t="inlineStr">
@@ -58749,7 +58661,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1484" t="inlineStr">
@@ -58788,7 +58700,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1485" t="inlineStr">
@@ -58827,7 +58739,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1486" t="inlineStr">
@@ -58866,7 +58778,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1487" t="inlineStr">
@@ -58905,7 +58817,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1488" t="inlineStr">
@@ -58944,7 +58856,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1489" t="inlineStr">
@@ -58983,7 +58895,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1490" t="inlineStr">
@@ -59139,7 +59051,7 @@
       </c>
       <c r="C1494" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1494" t="inlineStr">
@@ -59178,7 +59090,7 @@
       </c>
       <c r="C1495" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1495" t="inlineStr">
@@ -59217,7 +59129,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1496" t="inlineStr">
@@ -59256,7 +59168,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Backpack</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
@@ -59451,7 +59363,7 @@
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
@@ -59490,7 +59402,7 @@
       </c>
       <c r="C1503" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Cookware</t>
         </is>
       </c>
       <c r="D1503" t="inlineStr">
@@ -59568,7 +59480,7 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
@@ -59607,7 +59519,7 @@
       </c>
       <c r="C1506" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Portable Power</t>
         </is>
       </c>
       <c r="D1506" t="inlineStr">
@@ -59782,11 +59694,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1510" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1510" t="inlineStr"/>
       <c r="I1510" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -59825,11 +59733,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1511" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1511" t="inlineStr"/>
       <c r="I1511" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -59868,11 +59772,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1512" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1512" t="inlineStr"/>
       <c r="I1512" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -59911,11 +59811,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1513" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1513" t="inlineStr"/>
       <c r="I1513" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -59954,11 +59850,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1514" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1514" t="inlineStr"/>
       <c r="I1514" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -59997,11 +59889,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1515" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1515" t="inlineStr"/>
       <c r="I1515" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -60040,11 +59928,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1516" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1516" t="inlineStr"/>
       <c r="I1516" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -60083,11 +59967,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1517" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1517" t="inlineStr"/>
       <c r="I1517" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -60126,11 +60006,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1518" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1518" t="inlineStr"/>
       <c r="I1518" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -60169,11 +60045,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H1519" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> →  → </t>
-        </is>
-      </c>
+      <c r="H1519" t="inlineStr"/>
       <c r="I1519" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -60973,7 +60845,7 @@
       </c>
       <c r="C1540" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D1540" t="inlineStr">
@@ -62026,7 +61898,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D1567" t="inlineStr">
@@ -62065,7 +61937,7 @@
       </c>
       <c r="C1568" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D1568" t="inlineStr">
@@ -62416,7 +62288,7 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -62533,7 +62405,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Chair</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -62572,7 +62444,7 @@
       </c>
       <c r="C1581" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Lighting</t>
         </is>
       </c>
       <c r="D1581" t="inlineStr">
@@ -63458,7 +63330,7 @@
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>FUSE DANCE CARDIO LEAN of LOW IMPACT Pilates WEIGHT LOSS Barre WORKOUT on a DVD!</t>
+          <t>CHROME Riverton LEATHER Bike ROAD CYCLING Shoes MENS Boy WOMEN sz MTB Flat PEDAL</t>
         </is>
       </c>
       <c r="B1605" t="inlineStr">
@@ -63493,7 +63365,7 @@
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>CHROME Riverton LEATHER Bike ROAD CYCLING Shoes MENS Boy WOMEN sz MTB Flat PEDAL</t>
+          <t>YU-GI-OH! Season 1 First VOL on a 3 DVD of JAPAN Anime YUGIOH Yugi CARTOON Video</t>
         </is>
       </c>
       <c r="B1606" t="inlineStr">
@@ -63528,7 +63400,7 @@
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>YU-GI-OH! Season 1 First VOL on a 3 DVD of JAPAN Anime YUGIOH Yugi CARTOON Video</t>
+          <t>FUSE DANCE CARDIO LEAN of LOW IMPACT Pilates WEIGHT LOSS Barre WORKOUT on a DVD!</t>
         </is>
       </c>
       <c r="B1607" t="inlineStr">
@@ -63563,7 +63435,7 @@
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>THE CHRISTMAS SHOES on a BLU-RAY of HOLIDAY Family BLESSING Hope SERIE Song BOOK</t>
+          <t>COLUMBIA Coolest COOL Omni FREEZE Zero WICK Sun SPF 50 Top SS T SHIRT Women size</t>
         </is>
       </c>
       <c r="B1608" t="inlineStr">
@@ -63598,7 +63470,7 @@
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>COLUMBIA Coolest COOL Omni FREEZE Zero WICK Sun SPF 50 Top SS T SHIRT Women size</t>
+          <t>THE CHRISTMAS SHOES on a BLU-RAY of HOLIDAY Family BLESSING Hope SERIE Song BOOK</t>
         </is>
       </c>
       <c r="B1609" t="inlineStr">
@@ -63633,7 +63505,7 @@
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>ELECTRIC LA TXOKO Round CAT EYE Polarized SUNGLASSES Nude &amp; OHM Bronze GRADIENT</t>
+          <t>MARMOT Eldridge TRAVEL Sun UPF Hiking QUICK Dry WINDOWPANE Plaid SHIRT Mens size</t>
         </is>
       </c>
       <c r="B1610" t="inlineStr">
@@ -63668,7 +63540,7 @@
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>MARMOT Eldridge TRAVEL Sun UPF Hiking QUICK Dry WINDOWPANE Plaid SHIRT Mens size</t>
+          <t>ELECTRIC LA TXOKO Round CAT EYE Polarized SUNGLASSES Nude &amp; OHM Bronze GRADIENT</t>
         </is>
       </c>
       <c r="B1611" t="inlineStr">
@@ -63703,7 +63575,7 @@
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>SESAME STREET C is for COOKING DVD of EDUCATION Learn CHILDREN Kid TV SHOW Video</t>
+          <t>DYNAFIT TLT7 CARBONIO Speed ALPINE TOURING at SKIMO Ski BOOTS 24.5 Mens size 6.5</t>
         </is>
       </c>
       <c r="B1612" t="inlineStr">
@@ -63738,7 +63610,7 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>GRAMICCI Stella HEMP Organic COTTON Stripe BUTTON Down COLLAR SHIRT Women MED LG</t>
+          <t>SESAME STREET C is for COOKING DVD of EDUCATION Learn CHILDREN Kid TV SHOW Video</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
@@ -63808,7 +63680,7 @@
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>GRAMICCI Stella HEMP Organic COTTON Stripe BUTTON DOWN Collar SHIRT Womens LARGE</t>
+          <t>GRAMICCI Stella HEMP Organic COTTON Stripe BUTTON Down COLLAR SHIRT Women MED LG</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
@@ -63843,7 +63715,7 @@
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>MOUNTAIN CLUB Full Zip INSULATED Ski FLEECE Snow JACKET Coat WOMEN size S M L XL</t>
+          <t>GRAMICCI Stella HEMP Organic COTTON Stripe BUTTON DOWN Collar SHIRT Womens LARGE</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
@@ -63878,7 +63750,7 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>TURBO Jam CARDIO PARTY Mix 3 Video FITNESS Dance on a DVD of WEIGHT LOSS Workout</t>
+          <t>SESAME STREET Elmos TRAVEL SONGS and GAMES a DVD of EDUCATION Kid CHILDREN Video</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -63913,7 +63785,7 @@
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>MALCOLM X on a DVD of The BLACK Civil RIGHTS LEADER Life STORY Islam US HISTORY!</t>
+          <t>TURBO Jam CARDIO PARTY Mix 3 Video FITNESS Dance on a DVD of WEIGHT LOSS Workout</t>
         </is>
       </c>
       <c r="B1618" t="inlineStr">
@@ -63948,7 +63820,7 @@
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>SESAME STREET Elmos TRAVEL SONGS and GAMES a DVD of EDUCATION Kid CHILDREN Video</t>
+          <t>MOUNTAIN CLUB Full Zip INSULATED Ski FLEECE Snow JACKET Coat WOMEN size S M L XL</t>
         </is>
       </c>
       <c r="B1619" t="inlineStr">
@@ -63983,7 +63855,7 @@
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>PRACTICAL APPLICATION of CHEN-Style TAIJI QUAN and WEAPON Series BROADSWORD DVD!</t>
+          <t>MALCOLM X on a DVD of The BLACK Civil RIGHTS LEADER Life STORY Islam US HISTORY!</t>
         </is>
       </c>
       <c r="B1620" t="inlineStr">
@@ -64053,7 +63925,7 @@
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>DYNAFIT TLT7 CARBONIO Speed ALPINE TOURING at SKIMO Ski BOOTS 24.5 Mens size 6.5</t>
+          <t>TURBO Jam CARDIO PARTY Mix 3 Dance FITNESS of WEIGHT LOSS Workout on a DVD Video</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
@@ -64088,7 +63960,7 @@
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>TURBO Jam CARDIO PARTY Mix 3 Dance FITNESS of WEIGHT LOSS Workout on a DVD Video</t>
+          <t>COMPLETE DANCE 4 DVD of WEIGHT LOSS Workout BRAZILIAN Cardio HIP HOP Latin URBAN</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
@@ -64123,7 +63995,7 @@
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>SUNLITE 26 Wide MOUNTAIN BIKE mtb TUBE 26x2.125-2.50 with 40mm PRESTA Valve STEM</t>
+          <t>PRACTICAL APPLICATION of CHEN-Style TAIJI QUAN and WEAPON Series BROADSWORD DVD!</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
@@ -64158,7 +64030,7 @@
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>MEMORIES Of The SWORD on a BLU-RAY Korea KOREAN WAR History MARTIAL ARTS Action!</t>
+          <t>TURBO JAM 3T Video RESISTANCE Training FITNESS Dance DVD of WEIGHT LOSS Workout!</t>
         </is>
       </c>
       <c r="B1625" t="inlineStr">
@@ -64193,7 +64065,7 @@
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>COMPLETE DANCE 4 DVD of WEIGHT LOSS Workout BRAZILIAN Cardio HIP HOP Latin URBAN</t>
+          <t>REVO CLAYTON Re 1040 Round POLARIZED SUNGLASSES Matte HONEY HORN &amp; GRAPHITE Lens</t>
         </is>
       </c>
       <c r="B1626" t="inlineStr">
@@ -64228,7 +64100,7 @@
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>TURBO JAM 3T Video RESISTANCE Training FITNESS Dance DVD of WEIGHT LOSS Workout!</t>
+          <t>LEGO The LEGENDS Of CHIMA Chi TRIBES and BETRAYALS on a 2 DVD Kid ANIMATED Toy &amp;</t>
         </is>
       </c>
       <c r="B1627" t="inlineStr">
@@ -64263,7 +64135,7 @@
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>LEGO The LEGENDS Of CHIMA Chi TRIBES and BETRAYALS on a 2 DVD Kid ANIMATED Toy &amp;</t>
+          <t>MEMORIES Of The SWORD on a BLU-RAY Korea KOREAN WAR History MARTIAL ARTS Action!</t>
         </is>
       </c>
       <c r="B1628" t="inlineStr">
@@ -64298,7 +64170,7 @@
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>BABY GENIUS UNDERWATER ADVENTURES on a DVD + MUSIC CD of CHILDRENS Kids LEARNING</t>
+          <t>SUNLITE 26 Wide MOUNTAIN BIKE mtb TUBE 26x2.125-2.50 with 40mm PRESTA Valve STEM</t>
         </is>
       </c>
       <c r="B1629" t="inlineStr">
@@ -64333,7 +64205,7 @@
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>REVO CLAYTON Re 1040 Round POLARIZED SUNGLASSES Matte HONEY HORN &amp; GRAPHITE Lens</t>
+          <t>The SWAN PRINCESS a MYSTERY Of The ENCHANTED TREASURE on DVD Kids ANIMATED NEST!</t>
         </is>
       </c>
       <c r="B1630" t="inlineStr">
@@ -64368,7 +64240,7 @@
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>RIP CURL Serpentina BANDEAU BIKINI Tie REMOVABLE D CUP Stretch TOP Women size XL</t>
+          <t>BABY GENIUS UNDERWATER ADVENTURES on a DVD + MUSIC CD of CHILDRENS Kids LEARNING</t>
         </is>
       </c>
       <c r="B1631" t="inlineStr">
@@ -64403,7 +64275,7 @@
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>The SWAN PRINCESS a MYSTERY Of The ENCHANTED TREASURE on DVD Kids ANIMATED NEST!</t>
+          <t>THE FIRM Video POWER BURN 45 a DVD of WEIGH LOSS Cardio FITNESS Exercise WORKOUT</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
@@ -64438,7 +64310,7 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>THE FIRM Video POWER BURN 45 a DVD of WEIGH LOSS Cardio FITNESS Exercise WORKOUT</t>
+          <t>PRACTICAL APPLICATION of CHEN-Style TAIJI QUAN and WEAPON Series DVD Broad Sword</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
@@ -64473,7 +64345,7 @@
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>PRACTICAL APPLICATION of CHEN-Style TAIJI QUAN and WEAPON Series DVD Broad Sword</t>
+          <t>RIP CURL Serpentina BANDEAU BIKINI Tie REMOVABLE D CUP Stretch TOP Women size XL</t>
         </is>
       </c>
       <c r="B1634" t="inlineStr">
@@ -64543,7 +64415,7 @@
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>TOAD&amp;Co Sleeveless DRESS Shirt ORGANIC COTTON Indigo Ridge WOMENS size SMALL New</t>
+          <t>VIKING The BERSERKERS on DVD of The BATTLE Saga HISTORY Fight COMBAT Hunt ACTION</t>
         </is>
       </c>
       <c r="B1636" t="inlineStr">
@@ -64613,7 +64485,7 @@
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>LEGO of DC Comics SUPER HERO Justice League DVD MiniFig TRICKSTER Toy MINIFIGURE</t>
+          <t>Wii ACTIVE More WORKOUTS The NINTENDO Exercise VIDEO GAME Fitness NUTRITION BOOK</t>
         </is>
       </c>
       <c r="B1638" t="inlineStr">
@@ -64648,7 +64520,7 @@
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>SMARTWOOL Midweight MERINO WOOL Sleeve POCKET uv SWEATER Jacket WOMEN size LARGE</t>
+          <t>SESAME STREET Play ALL DAY with ELMO of CHILDREN Kid EDUCATION Video TV Show DVD</t>
         </is>
       </c>
       <c r="B1639" t="inlineStr">
@@ -64683,7 +64555,7 @@
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>VIKING The BERSERKERS on DVD of The BATTLE Saga HISTORY Fight COMBAT Hunt ACTION</t>
+          <t>HAWKE Flex MIDWEIGHT Insulated SOFTSHELL JACKET Parka COAT Hood MEN size XL $195</t>
         </is>
       </c>
       <c r="B1640" t="inlineStr">
@@ -64718,7 +64590,7 @@
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>BLONDO Tall WATERPROOF Leather INSULATED Zip RIDING Winter BOOTS Womens size 6.5</t>
+          <t>HOLIDAY BAGGAGE on a DVD of FAMILY Kids DIVORCE Video CHRISTMAS with CHERYL LADD</t>
         </is>
       </c>
       <c r="B1641" t="inlineStr">
@@ -64753,7 +64625,7 @@
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>HAWKE Flex MIDWEIGHT Insulated SOFTSHELL JACKET Parka COAT Hood MEN size XL $195</t>
+          <t>LEGO of DC Comics SUPER HERO Justice League DVD MiniFig TRICKSTER Toy MINIFIGURE</t>
         </is>
       </c>
       <c r="B1642" t="inlineStr">
@@ -64788,7 +64660,7 @@
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>CHACO Updraft Bulloo WATER Sport SANDALS Hiking STRAP Sandles SHOES Mens size 15</t>
+          <t>BANDEAU Bikini TOP Bra SPERRY Top-Sider SWIMSUIT Swim SWIMWEAR Beach IVORY Olive</t>
         </is>
       </c>
       <c r="B1643" t="inlineStr">
@@ -64823,7 +64695,7 @@
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>URBAN EXPRESSIONS Fit TOTE BAG Purse EXPANDABLE Vegan YOGA Spa SHOULDER HandBag!</t>
+          <t>ISABELLE DANCES into THE SPOTLIGHT a AMERICAN GIRL on DVD of CHILDREN Kid BALLET</t>
         </is>
       </c>
       <c r="B1644" t="inlineStr">
@@ -64858,7 +64730,7 @@
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>BANDEAU Bikini TOP Bra SPERRY Top-Sider SWIMSUIT Swim SWIMWEAR Beach IVORY Olive</t>
+          <t>TAKE THIS WALTZ on DVD of MARRIAGE Infidelity DRAMA Comedy with SARAH SILVERMAN!</t>
         </is>
       </c>
       <c r="B1645" t="inlineStr">
